--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/дв 13,07,26 днрсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/дв 13,07,26 днрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CECB6CF-DE25-4351-A6AA-E05059A1F810}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B26092-B7D0-4565-8FCC-EEE1357FA9EB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t>ВНИМАНИЕ акция</t>
-  </si>
-  <si>
-    <t>07,07,26 +600шт в заказ (просьба Босых под сети)</t>
   </si>
   <si>
     <t>5544 Сервелат Финский в/к в/у_45с НОВАЯ ОСТАНКИНО</t>
@@ -530,6 +527,9 @@
   <si>
     <t>пересчет +155кг (12,07,26)</t>
   </si>
+  <si>
+    <t>14,07,26 ноль (Босых) / 07,07,26 +600шт в заказ (просьба Босых под сети)</t>
+  </si>
 </sst>
 </file>
 
@@ -658,7 +658,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -678,6 +678,7 @@
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1327,7 +1328,7 @@
       </c>
       <c r="R5" s="5">
         <f t="shared" si="0"/>
-        <v>12229.686000000003</v>
+        <v>11729.686000000003</v>
       </c>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
@@ -1362,7 +1363,7 @@
       <c r="AB5" s="6"/>
       <c r="AC5" s="5">
         <f>SUM(AC6:AC493)</f>
-        <v>6683.7140000000018</v>
+        <v>6483.7140000000018</v>
       </c>
       <c r="AD5" s="6"/>
       <c r="AE5" s="6"/>
@@ -1754,7 +1755,7 @@
         <v>179.56120000000001</v>
       </c>
       <c r="R9" s="10">
-        <f t="shared" ref="R7:R17" si="7">15*Q9-P9-O9-F9</f>
+        <f t="shared" ref="R9:R17" si="7">15*Q9-P9-O9-F9</f>
         <v>779.2170000000001</v>
       </c>
       <c r="S9" s="6">
@@ -2481,12 +2482,12 @@
         <f t="shared" si="3"/>
         <v>271.2</v>
       </c>
-      <c r="R16" s="10">
-        <v>500</v>
+      <c r="R16" s="19">
+        <v>0</v>
       </c>
       <c r="S16" s="6">
         <f t="shared" si="4"/>
-        <v>5.8591445427728619</v>
+        <v>4.0154867256637168</v>
       </c>
       <c r="T16" s="6">
         <f t="shared" si="5"/>
@@ -2513,12 +2514,12 @@
       <c r="AA16" s="6">
         <v>74.8</v>
       </c>
-      <c r="AB16" s="6" t="s">
-        <v>48</v>
+      <c r="AB16" s="16" t="s">
+        <v>165</v>
       </c>
       <c r="AC16" s="6">
         <f t="shared" si="6"/>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="6"/>
       <c r="AE16" s="6"/>
@@ -2542,7 +2543,7 @@
     </row>
     <row r="17" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>34</v>
@@ -2646,7 +2647,7 @@
     </row>
     <row r="18" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>32</v>
@@ -2664,7 +2665,7 @@
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J18" s="14" t="s">
         <v>36</v>
@@ -2738,7 +2739,7 @@
     </row>
     <row r="19" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>34</v>
@@ -2841,7 +2842,7 @@
     </row>
     <row r="20" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>32</v>
@@ -2888,7 +2889,7 @@
         <v>56.6</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" ref="R19:R27" si="9">15*Q20-P20-O20-F20</f>
+        <f t="shared" ref="R20:R26" si="9">15*Q20-P20-O20-F20</f>
         <v>125</v>
       </c>
       <c r="S20" s="6">
@@ -2947,7 +2948,7 @@
     </row>
     <row r="21" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>34</v>
@@ -3052,7 +3053,7 @@
     </row>
     <row r="22" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>32</v>
@@ -3160,7 +3161,7 @@
     </row>
     <row r="23" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>34</v>
@@ -3261,7 +3262,7 @@
     </row>
     <row r="24" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>32</v>
@@ -3365,7 +3366,7 @@
     </row>
     <row r="25" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>34</v>
@@ -3469,7 +3470,7 @@
     </row>
     <row r="26" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>32</v>
@@ -3575,7 +3576,7 @@
     </row>
     <row r="27" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>32</v>
@@ -3678,7 +3679,7 @@
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>32</v>
@@ -3698,10 +3699,10 @@
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K28" s="12">
         <v>10</v>
@@ -3774,7 +3775,7 @@
     </row>
     <row r="29" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>32</v>
@@ -3877,7 +3878,7 @@
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>34</v>
@@ -3923,7 +3924,7 @@
         <v>40.973200000000006</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" ref="R29:R30" si="10">15*Q30-P30-O30-F30</f>
+        <f t="shared" ref="R30" si="10">15*Q30-P30-O30-F30</f>
         <v>199.02600000000007</v>
       </c>
       <c r="S30" s="6">
@@ -3982,7 +3983,7 @@
     </row>
     <row r="31" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>32</v>
@@ -4000,10 +4001,10 @@
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J31" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="K31" s="12">
         <v>270</v>
@@ -4074,7 +4075,7 @@
     </row>
     <row r="32" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>32</v>
@@ -4178,7 +4179,7 @@
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>32</v>
@@ -4282,7 +4283,7 @@
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>32</v>
@@ -4302,10 +4303,10 @@
         <v>60</v>
       </c>
       <c r="I34" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="J34" s="12" t="s">
         <v>71</v>
-      </c>
-      <c r="J34" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="K34" s="12">
         <v>240.3</v>
@@ -4353,7 +4354,7 @@
         <v>131.80000000000001</v>
       </c>
       <c r="AB34" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AC34" s="12"/>
       <c r="AD34" s="6"/>
@@ -4378,7 +4379,7 @@
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>32</v>
@@ -4484,7 +4485,7 @@
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>32</v>
@@ -4508,10 +4509,10 @@
         <v>60</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K36" s="12">
         <v>294</v>
@@ -4559,7 +4560,7 @@
         <v>47.6</v>
       </c>
       <c r="AB36" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AC36" s="12"/>
       <c r="AD36" s="6"/>
@@ -4584,7 +4585,7 @@
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>32</v>
@@ -4608,7 +4609,7 @@
         <v>60</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J37" s="6"/>
       <c r="K37" s="6">
@@ -4662,7 +4663,7 @@
         <v>48.2</v>
       </c>
       <c r="AB37" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC37" s="6">
         <f>G37*R37</f>
@@ -4690,7 +4691,7 @@
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>32</v>
@@ -4714,10 +4715,10 @@
         <v>45</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K38" s="12">
         <v>24</v>
@@ -4767,7 +4768,7 @@
         <v>13.2</v>
       </c>
       <c r="AB38" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AC38" s="12"/>
       <c r="AD38" s="6"/>
@@ -4792,7 +4793,7 @@
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>34</v>
@@ -4863,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="AB39" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC39" s="6">
         <f t="shared" ref="AC39:AC66" si="16">G39*R39</f>
@@ -4891,7 +4892,7 @@
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>32</v>
@@ -4995,7 +4996,7 @@
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>32</v>
@@ -5040,7 +5041,7 @@
         <v>29.6</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" ref="R39:R66" si="17">15*Q41-P41-O41-F41</f>
+        <f t="shared" ref="R41:R66" si="17">15*Q41-P41-O41-F41</f>
         <v>269</v>
       </c>
       <c r="S41" s="6">
@@ -5099,7 +5100,7 @@
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>34</v>
@@ -5200,7 +5201,7 @@
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>34</v>
@@ -5304,7 +5305,7 @@
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>34</v>
@@ -5408,7 +5409,7 @@
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>34</v>
@@ -5512,7 +5513,7 @@
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>32</v>
@@ -5615,7 +5616,7 @@
     </row>
     <row r="47" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>34</v>
@@ -5690,7 +5691,7 @@
         <v>2.7833999999999999</v>
       </c>
       <c r="AB47" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC47" s="6">
         <f t="shared" si="16"/>
@@ -5718,7 +5719,7 @@
     </row>
     <row r="48" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>32</v>
@@ -5821,7 +5822,7 @@
     </row>
     <row r="49" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>32</v>
@@ -5922,7 +5923,7 @@
     </row>
     <row r="50" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>32</v>
@@ -6026,7 +6027,7 @@
     </row>
     <row r="51" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>32</v>
@@ -6129,7 +6130,7 @@
     </row>
     <row r="52" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>32</v>
@@ -6230,7 +6231,7 @@
     </row>
     <row r="53" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>32</v>
@@ -6334,7 +6335,7 @@
     </row>
     <row r="54" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>32</v>
@@ -6437,7 +6438,7 @@
     </row>
     <row r="55" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>34</v>
@@ -6541,7 +6542,7 @@
     </row>
     <row r="56" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>34</v>
@@ -6642,7 +6643,7 @@
     </row>
     <row r="57" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>32</v>
@@ -6737,7 +6738,7 @@
     </row>
     <row r="58" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>32</v>
@@ -6840,7 +6841,7 @@
     </row>
     <row r="59" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>34</v>
@@ -6942,7 +6943,7 @@
     </row>
     <row r="60" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>34</v>
@@ -7046,7 +7047,7 @@
     </row>
     <row r="61" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>32</v>
@@ -7148,7 +7149,7 @@
     </row>
     <row r="62" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>34</v>
@@ -7246,7 +7247,7 @@
     </row>
     <row r="63" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>32</v>
@@ -7352,7 +7353,7 @@
     </row>
     <row r="64" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>34</v>
@@ -7456,7 +7457,7 @@
     </row>
     <row r="65" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>32</v>
@@ -7558,7 +7559,7 @@
     </row>
     <row r="66" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>32</v>
@@ -7666,7 +7667,7 @@
     </row>
     <row r="67" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>32</v>
@@ -7688,10 +7689,10 @@
       </c>
       <c r="H67" s="12"/>
       <c r="I67" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K67" s="12">
         <v>351</v>
@@ -7764,7 +7765,7 @@
     </row>
     <row r="68" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>34</v>
@@ -7870,7 +7871,7 @@
     </row>
     <row r="69" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>32</v>
@@ -7974,7 +7975,7 @@
     </row>
     <row r="70" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>32</v>
@@ -7992,10 +7993,10 @@
       </c>
       <c r="H70" s="12"/>
       <c r="I70" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J70" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K70" s="12">
         <v>18</v>
@@ -8066,7 +8067,7 @@
     </row>
     <row r="71" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>32</v>
@@ -8090,7 +8091,7 @@
         <v>50</v>
       </c>
       <c r="I71" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J71" s="6"/>
       <c r="K71" s="6">
@@ -8145,7 +8146,7 @@
         <v>136.80000000000001</v>
       </c>
       <c r="AB71" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AC71" s="6">
         <f>G71*R71</f>
@@ -8173,7 +8174,7 @@
     </row>
     <row r="72" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>34</v>
@@ -8191,10 +8192,10 @@
       </c>
       <c r="H72" s="12"/>
       <c r="I72" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J72" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K72" s="12">
         <v>9</v>
@@ -8267,7 +8268,7 @@
     </row>
     <row r="73" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>34</v>
@@ -8312,7 +8313,7 @@
         <v>19.265799999999999</v>
       </c>
       <c r="R73" s="10">
-        <f t="shared" ref="R73:R90" si="23">15*Q73-P73-O73-F73</f>
+        <f t="shared" ref="R73:R88" si="23">15*Q73-P73-O73-F73</f>
         <v>114.19799999999998</v>
       </c>
       <c r="S73" s="6">
@@ -8371,7 +8372,7 @@
     </row>
     <row r="74" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>32</v>
@@ -8471,7 +8472,7 @@
     </row>
     <row r="75" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>32</v>
@@ -8577,7 +8578,7 @@
     </row>
     <row r="76" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>32</v>
@@ -8678,7 +8679,7 @@
     </row>
     <row r="77" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>32</v>
@@ -8781,7 +8782,7 @@
     </row>
     <row r="78" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>34</v>
@@ -8885,7 +8886,7 @@
     </row>
     <row r="79" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>32</v>
@@ -8982,7 +8983,7 @@
     </row>
     <row r="80" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>34</v>
@@ -9086,7 +9087,7 @@
     </row>
     <row r="81" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>32</v>
@@ -9192,7 +9193,7 @@
     </row>
     <row r="82" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>32</v>
@@ -9296,7 +9297,7 @@
     </row>
     <row r="83" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>32</v>
@@ -9400,7 +9401,7 @@
     </row>
     <row r="84" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>32</v>
@@ -9504,7 +9505,7 @@
     </row>
     <row r="85" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>32</v>
@@ -9608,7 +9609,7 @@
     </row>
     <row r="86" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>32</v>
@@ -9712,7 +9713,7 @@
     </row>
     <row r="87" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>32</v>
@@ -9815,7 +9816,7 @@
     </row>
     <row r="88" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>32</v>
@@ -9920,7 +9921,7 @@
     </row>
     <row r="89" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>32</v>
@@ -10023,7 +10024,7 @@
     </row>
     <row r="90" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>32</v>
@@ -10127,7 +10128,7 @@
     </row>
     <row r="91" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>32</v>
@@ -10151,10 +10152,10 @@
         <v>60</v>
       </c>
       <c r="I91" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J91" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K91" s="12">
         <v>34</v>
@@ -10204,7 +10205,7 @@
         <v>5.2</v>
       </c>
       <c r="AB91" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AC91" s="12"/>
       <c r="AD91" s="6"/>
@@ -10229,7 +10230,7 @@
     </row>
     <row r="92" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>34</v>
@@ -10292,7 +10293,7 @@
         <v>0</v>
       </c>
       <c r="AB92" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AC92" s="6">
         <f t="shared" ref="AC92:AC108" si="25">G92*R92</f>
@@ -10320,7 +10321,7 @@
     </row>
     <row r="93" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>32</v>
@@ -10363,7 +10364,7 @@
         <v>3.6</v>
       </c>
       <c r="R93" s="10">
-        <f t="shared" ref="R92:R108" si="26">15*Q93-P93-O93-F93</f>
+        <f t="shared" ref="R93:R106" si="26">15*Q93-P93-O93-F93</f>
         <v>17</v>
       </c>
       <c r="S93" s="6">
@@ -10422,7 +10423,7 @@
     </row>
     <row r="94" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>32</v>
@@ -10525,7 +10526,7 @@
     </row>
     <row r="95" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>32</v>
@@ -10629,7 +10630,7 @@
     </row>
     <row r="96" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>32</v>
@@ -10708,7 +10709,7 @@
         <v>34.200000000000003</v>
       </c>
       <c r="AB96" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AC96" s="6">
         <f t="shared" si="25"/>
@@ -10736,7 +10737,7 @@
     </row>
     <row r="97" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>32</v>
@@ -10839,7 +10840,7 @@
     </row>
     <row r="98" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>32</v>
@@ -10938,7 +10939,7 @@
     </row>
     <row r="99" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>32</v>
@@ -11043,7 +11044,7 @@
     </row>
     <row r="100" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>32</v>
@@ -11117,7 +11118,7 @@
         <v>0</v>
       </c>
       <c r="AB100" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AC100" s="6">
         <f t="shared" si="25"/>
@@ -11145,7 +11146,7 @@
     </row>
     <row r="101" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>34</v>
@@ -11221,7 +11222,7 @@
         <v>2.8502000000000001</v>
       </c>
       <c r="AB101" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AC101" s="6">
         <f t="shared" si="25"/>
@@ -11249,7 +11250,7 @@
     </row>
     <row r="102" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>32</v>
@@ -11325,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="AB102" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AC102" s="6">
         <f t="shared" si="25"/>
@@ -11353,7 +11354,7 @@
     </row>
     <row r="103" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>32</v>
@@ -11424,7 +11425,7 @@
         <v>0</v>
       </c>
       <c r="AB103" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AC103" s="6">
         <f t="shared" si="25"/>
@@ -11452,7 +11453,7 @@
     </row>
     <row r="104" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>32</v>
@@ -11523,7 +11524,7 @@
         <v>0</v>
       </c>
       <c r="AB104" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AC104" s="6">
         <f t="shared" si="25"/>
@@ -11551,7 +11552,7 @@
     </row>
     <row r="105" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>32</v>
@@ -11629,7 +11630,7 @@
         <v>0</v>
       </c>
       <c r="AB105" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AC105" s="6">
         <f t="shared" si="25"/>
@@ -11657,7 +11658,7 @@
     </row>
     <row r="106" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>32</v>
@@ -11736,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="AB106" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AC106" s="6">
         <f t="shared" si="25"/>
@@ -11764,7 +11765,7 @@
     </row>
     <row r="107" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>32</v>
@@ -11827,7 +11828,7 @@
         <v>0</v>
       </c>
       <c r="AB107" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AC107" s="6">
         <f t="shared" si="25"/>
@@ -11855,7 +11856,7 @@
     </row>
     <row r="108" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>32</v>
@@ -11918,7 +11919,7 @@
         <v>0</v>
       </c>
       <c r="AB108" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AC108" s="6">
         <f t="shared" si="25"/>
@@ -11946,7 +11947,7 @@
     </row>
     <row r="109" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>34</v>
@@ -11964,10 +11965,10 @@
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J109" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K109" s="12"/>
       <c r="L109" s="12">
@@ -12038,7 +12039,7 @@
     </row>
     <row r="110" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>32</v>
@@ -12056,10 +12057,10 @@
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J110" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K110" s="12">
         <v>2</v>
@@ -12132,7 +12133,7 @@
     </row>
     <row r="111" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B111" s="12" t="s">
         <v>34</v>
@@ -12152,10 +12153,10 @@
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J111" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K111" s="12">
         <v>27.1</v>
